--- a/ERPDirectory/invoices.xlsx
+++ b/ERPDirectory/invoices.xlsx
@@ -531,10 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Promise Received</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -605,10 +609,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Promise Received</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -642,10 +650,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Promise Received</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
